--- a/output/dividend_champion.xlsx
+++ b/output/dividend_champion.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:Y32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,100 +429,115 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>cash_from_operations_cr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>net_profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>roce_percentage</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>market_cap_crore</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pe_ratio</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>net_profit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>opm_percentage</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>broad_sector</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>dividend_payout_ratio_pct</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>roce_percentage</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>market_cap_crore</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>pe_ratio</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>pb_ratio</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>net_profit</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>opm_percentage</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>broad_sector</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>dividend_payout_ratio_pct</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>sector_relative_score</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>revenue_cagr_3yr</t>
         </is>
@@ -531,7 +546,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -540,66 +555,75 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.09</v>
+        <v>8226</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>58.33</v>
+        <v>3816.58</v>
       </c>
       <c r="F2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="G2" t="n">
-        <v>11372</v>
+        <v>270.88</v>
       </c>
       <c r="H2" t="n">
-        <v>10.78</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>24.54</v>
+        <v>1814</v>
       </c>
       <c r="J2" t="n">
-        <v>29.46</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>85.44</v>
+        <v>26.49</v>
       </c>
       <c r="L2" t="n">
-        <v>17.3</v>
+        <v>26.64</v>
       </c>
       <c r="M2" t="n">
-        <v>1339586.09</v>
+        <v>38.9</v>
       </c>
       <c r="N2" t="n">
-        <v>37.9</v>
+        <v>2643616.86</v>
       </c>
       <c r="O2" t="n">
-        <v>6.71</v>
+        <v>71.89</v>
       </c>
       <c r="P2" t="n">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>48497</v>
+        <v>2.77</v>
       </c>
       <c r="R2" t="n">
-        <v>9610</v>
+        <v>30381</v>
       </c>
       <c r="S2" t="n">
-        <v>28</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>34</v>
+        <v>7595</v>
+      </c>
+      <c r="T2" t="n">
+        <v>32</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
       </c>
       <c r="V2" t="n">
-        <v>13.12675558948349</v>
+        <v>31</v>
+      </c>
+      <c r="W2" t="n">
+        <v>73.81911299270061</v>
+      </c>
+      <c r="X2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>9.909701355201484</v>
       </c>
     </row>
     <row r="3">
@@ -614,72 +638,81 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>21183</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="E3" t="n">
         <v>892.5700000000001</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.02</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>22.61</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>56.39</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>9424</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>19.31</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>120.69</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>121.24</v>
       </c>
-      <c r="K3" t="n">
-        <v>85.27</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>24.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1040632.92</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>76.23</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>7.87</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>4.27</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>68904</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>8167</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>16331</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
+        <v>70.21066259469271</v>
+      </c>
+      <c r="X3" t="n">
+        <v>90.24625159260717</v>
+      </c>
+      <c r="Y3" t="n">
         <v>67.58091776468258</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -688,72 +721,81 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>117.75</v>
+        <v>26122</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>4.84</v>
       </c>
       <c r="E4" t="n">
-        <v>41.19</v>
+        <v>49.45</v>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2938</v>
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="H4" t="n">
-        <v>14.55</v>
+        <v>0.16</v>
       </c>
       <c r="I4" t="n">
-        <v>14.85</v>
+        <v>853</v>
       </c>
       <c r="J4" t="n">
-        <v>15.44</v>
+        <v>8.16</v>
       </c>
       <c r="K4" t="n">
-        <v>84.19</v>
-      </c>
-      <c r="L4" t="n">
-        <v>185.43</v>
-      </c>
+        <v>73.18000000000001</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>1677775.19</v>
+        <v>63.79</v>
       </c>
       <c r="N4" t="n">
-        <v>54.96</v>
+        <v>183583.67</v>
       </c>
       <c r="O4" t="n">
-        <v>14.34</v>
+        <v>30.67</v>
       </c>
       <c r="P4" t="n">
-        <v>3.85</v>
+        <v>8.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>24394</v>
+        <v>3.77</v>
       </c>
       <c r="R4" t="n">
-        <v>3933</v>
+        <v>845966</v>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>79</v>
+        <v>40916</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
       </c>
       <c r="V4" t="n">
-        <v>18.28200866249903</v>
+        <v>15</v>
+      </c>
+      <c r="W4" t="n">
+        <v>69.35193867952822</v>
+      </c>
+      <c r="X4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.981735429882496</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -762,72 +804,81 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.79</v>
+        <v>4175</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09</v>
+        <v>16.12</v>
       </c>
       <c r="E5" t="n">
-        <v>87.52</v>
+        <v>117.75</v>
       </c>
       <c r="F5" t="n">
-        <v>1.13</v>
+        <v>0.1</v>
       </c>
       <c r="G5" t="n">
-        <v>20117</v>
+        <v>41.19</v>
       </c>
       <c r="H5" t="n">
-        <v>13.2</v>
+        <v>2.32</v>
       </c>
       <c r="I5" t="n">
-        <v>11.24</v>
+        <v>2938</v>
       </c>
       <c r="J5" t="n">
-        <v>12.47</v>
+        <v>14.55</v>
       </c>
       <c r="K5" t="n">
-        <v>83.59</v>
+        <v>14.85</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>15.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1112279.92</v>
+        <v>185.43</v>
       </c>
       <c r="N5" t="n">
-        <v>35.99</v>
+        <v>1677775.19</v>
       </c>
       <c r="O5" t="n">
-        <v>8.970000000000001</v>
+        <v>54.96</v>
       </c>
       <c r="P5" t="n">
-        <v>4.1</v>
+        <v>14.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>153670</v>
+        <v>3.85</v>
       </c>
       <c r="R5" t="n">
-        <v>26248</v>
+        <v>24394</v>
       </c>
       <c r="S5" t="n">
+        <v>3933</v>
+      </c>
+      <c r="T5" t="n">
         <v>24</v>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
       </c>
       <c r="V5" t="n">
-        <v>15.21650079880636</v>
+        <v>79</v>
+      </c>
+      <c r="W5" t="n">
+        <v>67.99817496750697</v>
+      </c>
+      <c r="X5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>18.28200866249903</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -836,66 +887,75 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3816.58</v>
+        <v>18103</v>
       </c>
       <c r="D6" t="n">
-        <v>0.62</v>
+        <v>26.26</v>
       </c>
       <c r="E6" t="n">
-        <v>270.88</v>
+        <v>45.17</v>
       </c>
       <c r="F6" t="n">
-        <v>67.51000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="G6" t="n">
-        <v>1814</v>
+        <v>11.24</v>
       </c>
       <c r="H6" t="n">
-        <v>8.710000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>26.49</v>
+        <v>13617</v>
       </c>
       <c r="J6" t="n">
-        <v>26.64</v>
+        <v>7.4</v>
       </c>
       <c r="K6" t="n">
-        <v>82.23</v>
+        <v>16.43</v>
       </c>
       <c r="L6" t="n">
-        <v>38.9</v>
+        <v>16.85</v>
       </c>
       <c r="M6" t="n">
-        <v>2643616.86</v>
+        <v>63.6</v>
       </c>
       <c r="N6" t="n">
-        <v>71.89</v>
+        <v>454024.84</v>
       </c>
       <c r="O6" t="n">
-        <v>3.65</v>
+        <v>34.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.77</v>
+        <v>14.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>30381</v>
+        <v>4.38</v>
       </c>
       <c r="R6" t="n">
-        <v>7595</v>
+        <v>142324</v>
       </c>
       <c r="S6" t="n">
-        <v>32</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>31</v>
+        <v>37369</v>
+      </c>
+      <c r="T6" t="n">
+        <v>47971</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
       </c>
       <c r="V6" t="n">
-        <v>9.909701355201484</v>
+        <v>42</v>
+      </c>
+      <c r="W6" t="n">
+        <v>65.97878967204697</v>
+      </c>
+      <c r="X6" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>16.49395652851666</v>
       </c>
     </row>
     <row r="7">
@@ -910,72 +970,81 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>1349</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="E7" t="n">
         <v>36.31</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>0.43</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>1.73</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>841</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>36.31</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>73.11</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>69.52</v>
       </c>
-      <c r="K7" t="n">
-        <v>80.95</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>23.8</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>571322.04</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>8.65</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>11.82</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>12375</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>1477</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>16</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>8</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
+        <v>65.57351320201516</v>
+      </c>
+      <c r="X7" t="n">
+        <v>78.61076524612234</v>
+      </c>
+      <c r="Y7" t="n">
         <v>68.36335197744833</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -984,72 +1053,81 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.68</v>
+        <v>5670</v>
       </c>
       <c r="D8" t="n">
-        <v>0.13</v>
+        <v>12.91</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>22.9</v>
       </c>
       <c r="F8" t="n">
-        <v>1.19</v>
+        <v>0.1</v>
       </c>
       <c r="G8" t="n">
-        <v>3556</v>
+        <v>31.93</v>
       </c>
       <c r="H8" t="n">
-        <v>13.03</v>
+        <v>1.29</v>
       </c>
       <c r="I8" t="n">
-        <v>20.28</v>
+        <v>1752</v>
       </c>
       <c r="J8" t="n">
-        <v>20.97</v>
+        <v>30.33</v>
       </c>
       <c r="K8" t="n">
-        <v>78.11</v>
+        <v>24.78</v>
       </c>
       <c r="L8" t="n">
-        <v>41.75</v>
+        <v>12.24</v>
       </c>
       <c r="M8" t="n">
-        <v>2126725.18</v>
+        <v>34.1</v>
       </c>
       <c r="N8" t="n">
-        <v>73.37</v>
+        <v>1347046.9</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>64.52</v>
       </c>
       <c r="P8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>35495</v>
+        <v>4.43</v>
       </c>
       <c r="R8" t="n">
-        <v>5558</v>
+        <v>35517</v>
       </c>
       <c r="S8" t="n">
-        <v>21</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>58</v>
+        <v>4585</v>
+      </c>
+      <c r="T8" t="n">
+        <v>18</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
       </c>
       <c r="V8" t="n">
-        <v>17.80103767695105</v>
+        <v>42</v>
+      </c>
+      <c r="W8" t="n">
+        <v>61.96385759189477</v>
+      </c>
+      <c r="X8" t="n">
+        <v>88.62519542917676</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>42.13101535214459</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1058,72 +1136,83 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>45.17</v>
+        <v>1941</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08</v>
+        <v>432.73</v>
       </c>
       <c r="E9" t="n">
-        <v>11.24</v>
+        <v>13.58</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13617</v>
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="H9" t="n">
-        <v>7.4</v>
+        <v>0.03</v>
       </c>
       <c r="I9" t="n">
-        <v>16.43</v>
+        <v>1469</v>
       </c>
       <c r="J9" t="n">
-        <v>16.85</v>
+        <v>31.61</v>
       </c>
       <c r="K9" t="n">
-        <v>75.5</v>
+        <v>19.3</v>
       </c>
       <c r="L9" t="n">
-        <v>63.6</v>
+        <v>18.97</v>
       </c>
       <c r="M9" t="n">
-        <v>454024.84</v>
+        <v>13.1</v>
       </c>
       <c r="N9" t="n">
-        <v>34.27</v>
+        <v>2191568.13</v>
       </c>
       <c r="O9" t="n">
-        <v>14.75</v>
+        <v>37.73</v>
       </c>
       <c r="P9" t="n">
-        <v>4.38</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>142324</v>
+        <v>3.37</v>
       </c>
       <c r="R9" t="n">
-        <v>37369</v>
+        <v>1702</v>
       </c>
       <c r="S9" t="n">
-        <v>47971</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>42</v>
+        <v>7365</v>
+      </c>
+      <c r="T9" t="n">
+        <v>92</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
       </c>
       <c r="V9" t="n">
-        <v>16.49395652851666</v>
+        <v>20</v>
+      </c>
+      <c r="W9" t="n">
+        <v>61.69365168186204</v>
+      </c>
+      <c r="X9" t="n">
+        <v>78.52118855546935</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>55.00574158769729</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1132,72 +1221,81 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.61</v>
+        <v>6104</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07000000000000001</v>
+        <v>15.66</v>
       </c>
       <c r="E10" t="n">
-        <v>174.42</v>
+        <v>29.68</v>
       </c>
       <c r="F10" t="n">
-        <v>1.14</v>
+        <v>0.13</v>
       </c>
       <c r="G10" t="n">
-        <v>6486</v>
+        <v>41</v>
       </c>
       <c r="H10" t="n">
-        <v>8.130000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="I10" t="n">
-        <v>9.359999999999999</v>
+        <v>3556</v>
       </c>
       <c r="J10" t="n">
-        <v>10.18</v>
+        <v>13.03</v>
       </c>
       <c r="K10" t="n">
-        <v>75.48</v>
+        <v>20.28</v>
       </c>
       <c r="L10" t="n">
-        <v>33.5</v>
+        <v>20.97</v>
       </c>
       <c r="M10" t="n">
-        <v>653817.3</v>
+        <v>41.75</v>
       </c>
       <c r="N10" t="n">
-        <v>29.91</v>
+        <v>2126725.18</v>
       </c>
       <c r="O10" t="n">
-        <v>9.83</v>
+        <v>73.37</v>
       </c>
       <c r="P10" t="n">
-        <v>3.59</v>
+        <v>3.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>44870</v>
+        <v>2.42</v>
       </c>
       <c r="R10" t="n">
-        <v>7708</v>
+        <v>35495</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U10" t="n">
-        <v>29</v>
+        <v>5558</v>
+      </c>
+      <c r="T10" t="n">
+        <v>21</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
       </c>
       <c r="V10" t="n">
-        <v>17.38465261667195</v>
+        <v>58</v>
+      </c>
+      <c r="W10" t="n">
+        <v>61.26515014988838</v>
+      </c>
+      <c r="X10" t="n">
+        <v>87.69272017291998</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>17.80103767695105</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1206,72 +1304,81 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17.87</v>
+        <v>25210</v>
       </c>
       <c r="D11" t="n">
-        <v>1.42</v>
+        <v>17.08</v>
       </c>
       <c r="E11" t="n">
-        <v>4.6</v>
+        <v>29.79</v>
       </c>
       <c r="F11" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="G11" t="n">
-        <v>24176</v>
+        <v>87.52</v>
       </c>
       <c r="H11" t="n">
-        <v>5.51</v>
+        <v>1.13</v>
       </c>
       <c r="I11" t="n">
-        <v>9.19</v>
+        <v>20117</v>
       </c>
       <c r="J11" t="n">
-        <v>9.1</v>
+        <v>13.2</v>
       </c>
       <c r="K11" t="n">
-        <v>75.15000000000001</v>
+        <v>11.24</v>
       </c>
       <c r="L11" t="n">
-        <v>13.2</v>
+        <v>12.47</v>
       </c>
       <c r="M11" t="n">
-        <v>372584.24</v>
+        <v>40</v>
       </c>
       <c r="N11" t="n">
-        <v>64.39</v>
+        <v>1112279.92</v>
       </c>
       <c r="O11" t="n">
-        <v>5.1</v>
+        <v>35.99</v>
       </c>
       <c r="P11" t="n">
-        <v>3.09</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>45843</v>
+        <v>4.1</v>
       </c>
       <c r="R11" t="n">
-        <v>15573</v>
+        <v>153670</v>
       </c>
       <c r="S11" t="n">
-        <v>87</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>67</v>
+        <v>26248</v>
+      </c>
+      <c r="T11" t="n">
+        <v>24</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
       </c>
       <c r="V11" t="n">
-        <v>4.965471644662767</v>
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>60.72864355840955</v>
+      </c>
+      <c r="X11" t="n">
+        <v>85.04353517246395</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>15.21650079880636</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1280,74 +1387,81 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13.58</v>
+        <v>3724</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>24.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>22.17</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G12" t="n">
-        <v>1469</v>
+        <v>114.71</v>
       </c>
       <c r="H12" t="n">
-        <v>31.61</v>
+        <v>0.72</v>
       </c>
       <c r="I12" t="n">
-        <v>19.3</v>
+        <v>890</v>
       </c>
       <c r="J12" t="n">
-        <v>18.97</v>
+        <v>11.04</v>
       </c>
       <c r="K12" t="n">
-        <v>74.64</v>
+        <v>12.68</v>
       </c>
       <c r="L12" t="n">
-        <v>13.1</v>
+        <v>12.51</v>
       </c>
       <c r="M12" t="n">
-        <v>2191568.13</v>
+        <v>31.1</v>
       </c>
       <c r="N12" t="n">
-        <v>37.73</v>
+        <v>222391.83</v>
       </c>
       <c r="O12" t="n">
-        <v>9.380000000000001</v>
+        <v>15.62</v>
       </c>
       <c r="P12" t="n">
-        <v>3.37</v>
+        <v>13.61</v>
       </c>
       <c r="Q12" t="n">
-        <v>1702</v>
+        <v>4.41</v>
       </c>
       <c r="R12" t="n">
-        <v>7365</v>
+        <v>16536</v>
       </c>
       <c r="S12" t="n">
-        <v>92</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U12" t="n">
-        <v>20</v>
+        <v>4001</v>
+      </c>
+      <c r="T12" t="n">
+        <v>26</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V12" t="n">
-        <v>55.00574158769729</v>
+        <v>35</v>
+      </c>
+      <c r="W12" t="n">
+        <v>57.92745860618593</v>
+      </c>
+      <c r="X12" t="n">
+        <v>59.42536569985521</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>23.776441520116</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1356,74 +1470,81 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.72</v>
+        <v>1695</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>6.84</v>
+      </c>
+      <c r="E13" t="n">
+        <v>37.22</v>
       </c>
       <c r="F13" t="n">
-        <v>0.32</v>
+        <v>1.65</v>
       </c>
       <c r="G13" t="n">
-        <v>486</v>
+        <v>9.41</v>
       </c>
       <c r="H13" t="n">
-        <v>12.91</v>
+        <v>1.62</v>
       </c>
       <c r="I13" t="n">
-        <v>12.84</v>
+        <v>1506</v>
       </c>
       <c r="J13" t="n">
-        <v>11.14</v>
+        <v>20.9</v>
       </c>
       <c r="K13" t="n">
-        <v>72.98</v>
+        <v>20.27</v>
       </c>
       <c r="L13" t="n">
-        <v>22.5</v>
+        <v>19.51</v>
       </c>
       <c r="M13" t="n">
-        <v>1271789.21</v>
+        <v>22.7</v>
       </c>
       <c r="N13" t="n">
-        <v>49</v>
+        <v>1793769.72</v>
       </c>
       <c r="O13" t="n">
-        <v>7.86</v>
+        <v>10.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>10.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>20487</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1919</v>
+        <v>51084</v>
       </c>
       <c r="S13" t="n">
-        <v>2577</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U13" t="n">
+        <v>3496</v>
+      </c>
+      <c r="T13" t="n">
+        <v>10</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
         <v>28</v>
       </c>
-      <c r="V13" t="n">
-        <v>18.98796206427069</v>
+      <c r="W13" t="n">
+        <v>57.18809014417658</v>
+      </c>
+      <c r="X13" t="n">
+        <v>57.57015015335676</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>33.14221885428872</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1432,72 +1553,81 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.9</v>
+        <v>6558</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>17.18</v>
       </c>
       <c r="E14" t="n">
-        <v>31.93</v>
+        <v>26.61</v>
       </c>
       <c r="F14" t="n">
-        <v>1.29</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1752</v>
+        <v>174.42</v>
       </c>
       <c r="H14" t="n">
-        <v>30.33</v>
+        <v>1.14</v>
       </c>
       <c r="I14" t="n">
-        <v>24.78</v>
+        <v>6486</v>
       </c>
       <c r="J14" t="n">
-        <v>12.24</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>72.55</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>34.1</v>
+        <v>10.18</v>
       </c>
       <c r="M14" t="n">
-        <v>1347046.9</v>
+        <v>33.5</v>
       </c>
       <c r="N14" t="n">
-        <v>64.52</v>
+        <v>653817.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>29.91</v>
       </c>
       <c r="P14" t="n">
-        <v>4.43</v>
+        <v>9.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>35517</v>
+        <v>3.59</v>
       </c>
       <c r="R14" t="n">
-        <v>4585</v>
+        <v>44870</v>
       </c>
       <c r="S14" t="n">
-        <v>18</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="U14" t="n">
-        <v>42</v>
+        <v>7708</v>
+      </c>
+      <c r="T14" t="n">
+        <v>20</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V14" t="n">
-        <v>42.13101535214459</v>
+        <v>29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>56.16710174675491</v>
+      </c>
+      <c r="X14" t="n">
+        <v>55.00829683526474</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>17.38465261667195</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1506,146 +1636,164 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.17</v>
+        <v>12135</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02</v>
+        <v>19.82</v>
       </c>
       <c r="E15" t="n">
-        <v>114.71</v>
+        <v>15.09</v>
       </c>
       <c r="F15" t="n">
-        <v>0.72</v>
+        <v>0.05</v>
       </c>
       <c r="G15" t="n">
-        <v>890</v>
+        <v>58.33</v>
       </c>
       <c r="H15" t="n">
-        <v>11.04</v>
+        <v>0.57</v>
       </c>
       <c r="I15" t="n">
-        <v>12.68</v>
+        <v>11372</v>
       </c>
       <c r="J15" t="n">
-        <v>12.51</v>
+        <v>10.78</v>
       </c>
       <c r="K15" t="n">
-        <v>72.52</v>
+        <v>24.54</v>
       </c>
       <c r="L15" t="n">
-        <v>31.1</v>
+        <v>29.46</v>
       </c>
       <c r="M15" t="n">
-        <v>222391.83</v>
+        <v>17.3</v>
       </c>
       <c r="N15" t="n">
-        <v>15.62</v>
+        <v>1339586.09</v>
       </c>
       <c r="O15" t="n">
-        <v>13.61</v>
+        <v>37.9</v>
       </c>
       <c r="P15" t="n">
-        <v>4.41</v>
+        <v>6.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>16536</v>
+        <v>3.88</v>
       </c>
       <c r="R15" t="n">
-        <v>4001</v>
+        <v>48497</v>
       </c>
       <c r="S15" t="n">
-        <v>26</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U15" t="n">
-        <v>35</v>
+        <v>9610</v>
+      </c>
+      <c r="T15" t="n">
+        <v>28</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
       </c>
       <c r="V15" t="n">
-        <v>23.776441520116</v>
+        <v>34</v>
+      </c>
+      <c r="W15" t="n">
+        <v>50.96536737685161</v>
+      </c>
+      <c r="X15" t="n">
+        <v>44.6485862749794</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.12675558948349</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mar 2024</t>
+          <t>Sep 2024</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.91</v>
+        <v>1670</v>
       </c>
       <c r="D16" t="n">
-        <v>0.12</v>
+        <v>12.22</v>
       </c>
       <c r="E16" t="n">
-        <v>7.46</v>
+        <v>17.7</v>
       </c>
       <c r="F16" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="G16" t="n">
-        <v>1010</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-5.14</v>
+        <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>15.7</v>
+        <v>1168</v>
       </c>
       <c r="J16" t="n">
-        <v>12.89</v>
+        <v>11.19</v>
       </c>
       <c r="K16" t="n">
-        <v>72.33</v>
+        <v>19.85</v>
       </c>
       <c r="L16" t="n">
-        <v>5.74</v>
+        <v>19.64</v>
       </c>
       <c r="M16" t="n">
-        <v>1381712.03</v>
+        <v>25.6</v>
       </c>
       <c r="N16" t="n">
-        <v>46.26</v>
+        <v>1191331.95</v>
       </c>
       <c r="O16" t="n">
-        <v>14.32</v>
+        <v>33.32</v>
       </c>
       <c r="P16" t="n">
-        <v>2.58</v>
+        <v>9.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>6427</v>
+        <v>3.69</v>
       </c>
       <c r="R16" t="n">
-        <v>2724</v>
+        <v>22240</v>
       </c>
       <c r="S16" t="n">
-        <v>33</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="U16" t="n">
-        <v>45</v>
+        <v>2718</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
       </c>
       <c r="V16" t="n">
-        <v>5.883921200220743</v>
+        <v>16</v>
+      </c>
+      <c r="W16" t="n">
+        <v>50.59396623685769</v>
+      </c>
+      <c r="X16" t="n">
+        <v>55.2180951266328</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>18.99870072744285</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1654,72 +1802,83 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18.36</v>
+        <v>2407</v>
       </c>
       <c r="D17" t="n">
-        <v>0.14</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>23.24</v>
+        <v>15.72</v>
       </c>
       <c r="F17" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1042</v>
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="H17" t="n">
-        <v>7.81</v>
+        <v>0.32</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>486</v>
       </c>
       <c r="J17" t="n">
-        <v>4.56</v>
+        <v>12.91</v>
       </c>
       <c r="K17" t="n">
-        <v>72.03</v>
+        <v>12.84</v>
       </c>
       <c r="L17" t="n">
-        <v>22.3</v>
+        <v>11.14</v>
       </c>
       <c r="M17" t="n">
-        <v>56521.84</v>
+        <v>22.5</v>
       </c>
       <c r="N17" t="n">
-        <v>50.95</v>
+        <v>1271789.21</v>
       </c>
       <c r="O17" t="n">
-        <v>13.59</v>
+        <v>49</v>
       </c>
       <c r="P17" t="n">
-        <v>3.42</v>
+        <v>7.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>12404</v>
+        <v>3.46</v>
       </c>
       <c r="R17" t="n">
-        <v>1811</v>
+        <v>20487</v>
       </c>
       <c r="S17" t="n">
-        <v>19</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="U17" t="n">
-        <v>53</v>
+        <v>1919</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2577</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
       </c>
       <c r="V17" t="n">
-        <v>9.061384362071356</v>
+        <v>28</v>
+      </c>
+      <c r="W17" t="n">
+        <v>49.39652873350715</v>
+      </c>
+      <c r="X17" t="n">
+        <v>44.03206779015759</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>18.98796206427069</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1728,72 +1887,81 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.369999999999999</v>
+        <v>157284</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08</v>
+        <v>28.89</v>
       </c>
       <c r="E18" t="n">
-        <v>19.83</v>
+        <v>17.99</v>
       </c>
       <c r="F18" t="n">
-        <v>0.73</v>
+        <v>6.45</v>
       </c>
       <c r="G18" t="n">
-        <v>1929</v>
+        <v>1.3</v>
       </c>
       <c r="H18" t="n">
-        <v>10.33</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>11.29</v>
+        <v>12547</v>
       </c>
       <c r="J18" t="n">
-        <v>10.68</v>
+        <v>17.25</v>
       </c>
       <c r="K18" t="n">
-        <v>71.61</v>
+        <v>51.95</v>
       </c>
       <c r="L18" t="n">
-        <v>14.8</v>
+        <v>55.18</v>
       </c>
       <c r="M18" t="n">
-        <v>3154358.33</v>
+        <v>7.6</v>
       </c>
       <c r="N18" t="n">
-        <v>25.87</v>
+        <v>1319221.86</v>
       </c>
       <c r="O18" t="n">
-        <v>1.21</v>
+        <v>25.76</v>
       </c>
       <c r="P18" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>20521</v>
+        <v>3.43</v>
       </c>
       <c r="R18" t="n">
-        <v>1733</v>
+        <v>159516</v>
       </c>
       <c r="S18" t="n">
-        <v>22</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="U18" t="n">
+        <v>46081</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-14152</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
         <v>16</v>
       </c>
-      <c r="V18" t="n">
-        <v>14.80997180241832</v>
+      <c r="W18" t="n">
+        <v>48.83992353907501</v>
+      </c>
+      <c r="X18" t="n">
+        <v>42.47098526296872</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>21.39660074377121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1802,66 +1970,75 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>49.45</v>
+        <v>1920</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>4.91</v>
+      </c>
+      <c r="E19" t="n">
+        <v>13.48</v>
       </c>
       <c r="F19" t="n">
-        <v>0.16</v>
+        <v>0.77</v>
       </c>
       <c r="G19" t="n">
-        <v>853</v>
+        <v>5.57</v>
       </c>
       <c r="H19" t="n">
-        <v>8.16</v>
+        <v>1.14</v>
       </c>
       <c r="I19" t="n">
-        <v>73.18000000000001</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
+        <v>383</v>
+      </c>
+      <c r="J19" t="n">
+        <v>14.66</v>
+      </c>
       <c r="K19" t="n">
-        <v>69.53</v>
+        <v>36.13</v>
       </c>
       <c r="L19" t="n">
-        <v>63.79</v>
+        <v>29.95</v>
       </c>
       <c r="M19" t="n">
-        <v>183583.67</v>
+        <v>17.2</v>
       </c>
       <c r="N19" t="n">
-        <v>30.67</v>
+        <v>1905622.43</v>
       </c>
       <c r="O19" t="n">
-        <v>8.1</v>
+        <v>47.72</v>
       </c>
       <c r="P19" t="n">
-        <v>3.77</v>
+        <v>7.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>845966</v>
+        <v>3.22</v>
       </c>
       <c r="R19" t="n">
-        <v>40916</v>
+        <v>19059</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>15</v>
+        <v>935</v>
+      </c>
+      <c r="T19" t="n">
+        <v>13</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
       </c>
       <c r="V19" t="n">
-        <v>6.981735429882496</v>
+        <v>26</v>
+      </c>
+      <c r="W19" t="n">
+        <v>47.48953980088782</v>
+      </c>
+      <c r="X19" t="n">
+        <v>7.620402450361002</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>21.75273635187671</v>
       </c>
     </row>
     <row r="20">
@@ -1876,74 +2053,83 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>1253</v>
+      </c>
+      <c r="D20" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="E20" t="n">
         <v>20.64</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
         <v>0.96</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>1536</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>6.72</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>9.26</v>
       </c>
-      <c r="K20" t="n">
-        <v>68.12</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>20.6</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>2599556.05</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>58.43</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6.47</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4.23</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>16727</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>2490</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>13</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>44</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
+        <v>45.64309856903565</v>
+      </c>
+      <c r="X20" t="n">
+        <v>28.60157906204023</v>
+      </c>
+      <c r="Y20" t="n">
         <v>19.843289373664</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1952,72 +2138,81 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13.48</v>
+        <v>1953</v>
       </c>
       <c r="D21" t="n">
-        <v>0.77</v>
+        <v>6.84</v>
       </c>
       <c r="E21" t="n">
-        <v>5.57</v>
+        <v>17.07</v>
       </c>
       <c r="F21" t="n">
-        <v>1.14</v>
+        <v>0.04</v>
       </c>
       <c r="G21" t="n">
-        <v>383</v>
+        <v>25.36</v>
       </c>
       <c r="H21" t="n">
-        <v>14.66</v>
+        <v>1.5</v>
       </c>
       <c r="I21" t="n">
-        <v>36.13</v>
+        <v>335</v>
       </c>
       <c r="J21" t="n">
-        <v>29.95</v>
+        <v>13.04</v>
       </c>
       <c r="K21" t="n">
-        <v>68.01000000000001</v>
+        <v>10.03</v>
       </c>
       <c r="L21" t="n">
-        <v>17.2</v>
+        <v>9</v>
       </c>
       <c r="M21" t="n">
-        <v>1905622.43</v>
+        <v>24.4</v>
       </c>
       <c r="N21" t="n">
-        <v>47.72</v>
+        <v>2521508.87</v>
       </c>
       <c r="O21" t="n">
-        <v>7.68</v>
+        <v>45.41</v>
       </c>
       <c r="P21" t="n">
-        <v>3.22</v>
+        <v>14.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>19059</v>
+        <v>2.6</v>
       </c>
       <c r="R21" t="n">
-        <v>935</v>
+        <v>18590</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>26</v>
+        <v>1271</v>
+      </c>
+      <c r="T21" t="n">
+        <v>10</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
       </c>
       <c r="V21" t="n">
-        <v>21.75273635187671</v>
+        <v>44</v>
+      </c>
+      <c r="W21" t="n">
+        <v>45.18874127254222</v>
+      </c>
+      <c r="X21" t="n">
+        <v>44.79593191208912</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>21.14089015706202</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2026,146 +2221,164 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9.960000000000001</v>
+        <v>19069</v>
       </c>
       <c r="D22" t="n">
-        <v>0.58</v>
+        <v>23.07</v>
       </c>
       <c r="E22" t="n">
-        <v>7.73</v>
+        <v>14.34</v>
       </c>
       <c r="F22" t="n">
-        <v>0.51</v>
+        <v>6.81</v>
       </c>
       <c r="G22" t="n">
-        <v>45207</v>
+        <v>1.4</v>
       </c>
       <c r="H22" t="n">
-        <v>9.609999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>14.68</v>
+        <v>35669</v>
       </c>
       <c r="J22" t="n">
-        <v>11.95</v>
+        <v>21.95</v>
       </c>
       <c r="K22" t="n">
-        <v>67.22</v>
+        <v>23.87</v>
       </c>
       <c r="L22" t="n">
-        <v>9.609999999999999</v>
+        <v>15.42</v>
       </c>
       <c r="M22" t="n">
-        <v>432472.71</v>
+        <v>7.67</v>
       </c>
       <c r="N22" t="n">
-        <v>58.34</v>
+        <v>808359.03</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>49.42</v>
       </c>
       <c r="P22" t="n">
-        <v>4.21</v>
+        <v>4.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>899041</v>
+        <v>4.33</v>
       </c>
       <c r="R22" t="n">
-        <v>79020</v>
+        <v>283649</v>
       </c>
       <c r="S22" t="n">
-        <v>18</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="U22" t="n">
-        <v>10</v>
+        <v>65446</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-44685</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
       </c>
       <c r="V22" t="n">
-        <v>24.46173600944801</v>
+        <v>23</v>
+      </c>
+      <c r="W22" t="n">
+        <v>44.08554497818926</v>
+      </c>
+      <c r="X22" t="n">
+        <v>29.13661940852842</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>30.18695614094877</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sep 2024</t>
+          <t>Mar 2024</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17.7</v>
+        <v>37290</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02</v>
+        <v>33.97</v>
       </c>
       <c r="E23" t="n">
-        <v>67.15000000000001</v>
+        <v>17.87</v>
       </c>
       <c r="F23" t="n">
-        <v>0.88</v>
+        <v>1.42</v>
       </c>
       <c r="G23" t="n">
-        <v>1168</v>
+        <v>4.6</v>
       </c>
       <c r="H23" t="n">
-        <v>11.19</v>
+        <v>0.18</v>
       </c>
       <c r="I23" t="n">
-        <v>19.85</v>
+        <v>24176</v>
       </c>
       <c r="J23" t="n">
-        <v>19.64</v>
+        <v>5.51</v>
       </c>
       <c r="K23" t="n">
-        <v>66.98</v>
+        <v>9.19</v>
       </c>
       <c r="L23" t="n">
-        <v>25.6</v>
+        <v>9.1</v>
       </c>
       <c r="M23" t="n">
-        <v>1191331.95</v>
+        <v>13.2</v>
       </c>
       <c r="N23" t="n">
-        <v>33.32</v>
+        <v>372584.24</v>
       </c>
       <c r="O23" t="n">
-        <v>9.25</v>
+        <v>64.39</v>
       </c>
       <c r="P23" t="n">
-        <v>3.69</v>
+        <v>5.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>22240</v>
+        <v>3.09</v>
       </c>
       <c r="R23" t="n">
-        <v>2718</v>
+        <v>45843</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="U23" t="n">
-        <v>16</v>
+        <v>15573</v>
+      </c>
+      <c r="T23" t="n">
+        <v>87</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
       </c>
       <c r="V23" t="n">
-        <v>18.99870072744285</v>
+        <v>67</v>
+      </c>
+      <c r="W23" t="n">
+        <v>43.49563094136326</v>
+      </c>
+      <c r="X23" t="n">
+        <v>36.58916194804204</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>4.965471644662767</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2174,72 +2387,77 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37.22</v>
+        <v>67915</v>
       </c>
       <c r="D24" t="n">
-        <v>1.65</v>
+        <v>7.26</v>
       </c>
       <c r="E24" t="n">
-        <v>9.41</v>
+        <v>37.46</v>
       </c>
       <c r="F24" t="n">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="G24" t="n">
-        <v>1506</v>
+        <v>6.53</v>
       </c>
       <c r="H24" t="n">
-        <v>20.9</v>
+        <v>1.19</v>
       </c>
       <c r="I24" t="n">
-        <v>20.27</v>
+        <v>45133</v>
       </c>
       <c r="J24" t="n">
-        <v>19.51</v>
-      </c>
-      <c r="K24" t="n">
-        <v>65.84</v>
-      </c>
-      <c r="L24" t="n">
-        <v>22.7</v>
-      </c>
+        <v>7.72</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>1793769.72</v>
+        <v>20.1</v>
       </c>
       <c r="N24" t="n">
-        <v>10.13</v>
+        <v>1504106.64</v>
       </c>
       <c r="O24" t="n">
-        <v>10.51</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>3.1</v>
+        <v>0.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>51084</v>
+        <v>3.65</v>
       </c>
       <c r="R24" t="n">
-        <v>3496</v>
+        <v>437928</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
+        <v>31807</v>
+      </c>
+      <c r="T24" t="n">
+        <v>14</v>
+      </c>
+      <c r="U24" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="U24" t="n">
-        <v>28</v>
-      </c>
       <c r="V24" t="n">
-        <v>33.14221885428872</v>
+        <v>7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>43.15698106698831</v>
+      </c>
+      <c r="X24" t="n">
+        <v>22.36343924784591</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>20.57936456937097</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2248,66 +2466,81 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.15</v>
+        <v>2013</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>14.6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>18.36</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="G25" t="n">
-        <v>763</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+        <v>23.24</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1042</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7.81</v>
+      </c>
       <c r="K25" t="n">
-        <v>65.13</v>
+        <v>4.6</v>
       </c>
       <c r="L25" t="n">
-        <v>2.16</v>
+        <v>4.56</v>
       </c>
       <c r="M25" t="n">
-        <v>1401774.99</v>
+        <v>22.3</v>
       </c>
       <c r="N25" t="n">
-        <v>34.24</v>
+        <v>56521.84</v>
       </c>
       <c r="O25" t="n">
-        <v>9.91</v>
+        <v>50.95</v>
       </c>
       <c r="P25" t="n">
-        <v>3.09</v>
+        <v>13.59</v>
       </c>
       <c r="Q25" t="n">
-        <v>1855</v>
+        <v>3.42</v>
       </c>
       <c r="R25" t="n">
-        <v>1605</v>
+        <v>12404</v>
       </c>
       <c r="S25" t="n">
-        <v>84</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="inlineStr"/>
+        <v>1811</v>
+      </c>
+      <c r="T25" t="n">
+        <v>19</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>53</v>
+      </c>
+      <c r="W25" t="n">
+        <v>43.11994843836734</v>
+      </c>
+      <c r="X25" t="n">
+        <v>36.67737238738353</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9.061384362071356</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2316,72 +2549,81 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17.07</v>
+        <v>15046</v>
       </c>
       <c r="D26" t="n">
-        <v>0.04</v>
+        <v>13.94</v>
       </c>
       <c r="E26" t="n">
-        <v>25.36</v>
+        <v>16.72</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5</v>
+        <v>14.87</v>
       </c>
       <c r="G26" t="n">
-        <v>335</v>
+        <v>1.61</v>
       </c>
       <c r="H26" t="n">
-        <v>13.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>10.03</v>
+        <v>13296</v>
       </c>
       <c r="J26" t="n">
-        <v>9</v>
+        <v>18.18</v>
       </c>
       <c r="K26" t="n">
-        <v>64.59999999999999</v>
+        <v>85.78</v>
       </c>
       <c r="L26" t="n">
-        <v>24.4</v>
+        <v>53.42</v>
       </c>
       <c r="M26" t="n">
-        <v>2521508.87</v>
+        <v>6.63</v>
       </c>
       <c r="N26" t="n">
-        <v>45.41</v>
+        <v>496415.88</v>
       </c>
       <c r="O26" t="n">
-        <v>14.08</v>
+        <v>36.74</v>
       </c>
       <c r="P26" t="n">
-        <v>2.6</v>
+        <v>12.61</v>
       </c>
       <c r="Q26" t="n">
-        <v>18590</v>
+        <v>3.81</v>
       </c>
       <c r="R26" t="n">
-        <v>1271</v>
+        <v>110519</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="U26" t="n">
-        <v>44</v>
+        <v>15401</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-7745</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
       </c>
       <c r="V26" t="n">
-        <v>21.14089015706202</v>
+        <v>19</v>
+      </c>
+      <c r="W26" t="n">
+        <v>42.60305121511472</v>
+      </c>
+      <c r="X26" t="n">
+        <v>24.97874389217935</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.30293930023252</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2390,72 +2632,75 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17.99</v>
+        <v>-678</v>
       </c>
       <c r="D27" t="n">
-        <v>6.45</v>
+        <v>86.52</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G27" t="n">
-        <v>12547</v>
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="H27" t="n">
-        <v>17.25</v>
+        <v>0.01</v>
       </c>
       <c r="I27" t="n">
-        <v>51.95</v>
-      </c>
-      <c r="J27" t="n">
-        <v>55.18</v>
-      </c>
-      <c r="K27" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="L27" t="n">
-        <v>7.6</v>
-      </c>
+        <v>763</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>1319221.86</v>
+        <v>2.16</v>
       </c>
       <c r="N27" t="n">
-        <v>25.76</v>
+        <v>1401774.99</v>
       </c>
       <c r="O27" t="n">
-        <v>6.2</v>
+        <v>34.24</v>
       </c>
       <c r="P27" t="n">
-        <v>3.43</v>
+        <v>9.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>159516</v>
+        <v>3.09</v>
       </c>
       <c r="R27" t="n">
-        <v>46081</v>
+        <v>1855</v>
       </c>
       <c r="S27" t="n">
-        <v>-14152</v>
-      </c>
-      <c r="T27" t="inlineStr">
+        <v>1605</v>
+      </c>
+      <c r="T27" t="n">
+        <v>84</v>
+      </c>
+      <c r="U27" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="U27" t="n">
-        <v>16</v>
-      </c>
       <c r="V27" t="n">
-        <v>21.39660074377121</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="X27" t="n">
+        <v>24.6897213445452</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2464,68 +2709,81 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37.46</v>
+        <v>7914</v>
       </c>
       <c r="D28" t="n">
-        <v>1.26</v>
+        <v>24.06</v>
       </c>
       <c r="E28" t="n">
-        <v>6.53</v>
+        <v>13.04</v>
       </c>
       <c r="F28" t="n">
-        <v>1.19</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>45133</v>
+        <v>1.32</v>
       </c>
       <c r="H28" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+        <v>0.05</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7906</v>
+      </c>
+      <c r="J28" t="n">
+        <v>19.07</v>
+      </c>
       <c r="K28" t="n">
-        <v>62.94</v>
+        <v>23.25</v>
       </c>
       <c r="L28" t="n">
-        <v>20.1</v>
+        <v>20.11</v>
       </c>
       <c r="M28" t="n">
-        <v>1504106.64</v>
+        <v>5.73</v>
       </c>
       <c r="N28" t="n">
-        <v>67.06999999999999</v>
+        <v>2618348.58</v>
       </c>
       <c r="O28" t="n">
-        <v>0.93</v>
+        <v>9.81</v>
       </c>
       <c r="P28" t="n">
-        <v>3.65</v>
+        <v>3.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>437928</v>
+        <v>2.82</v>
       </c>
       <c r="R28" t="n">
-        <v>31807</v>
+        <v>26645</v>
       </c>
       <c r="S28" t="n">
-        <v>14</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U28" t="n">
-        <v>7</v>
+        <v>6412</v>
+      </c>
+      <c r="T28" t="n">
+        <v>100</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
       </c>
       <c r="V28" t="n">
-        <v>20.57936456937097</v>
+        <v>31</v>
+      </c>
+      <c r="W28" t="n">
+        <v>42.28401740380991</v>
+      </c>
+      <c r="X28" t="n">
+        <v>24.08396584592249</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>19.10193873049559</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2534,72 +2792,81 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.72</v>
+        <v>2539</v>
       </c>
       <c r="D29" t="n">
-        <v>14.87</v>
+        <v>42.38</v>
       </c>
       <c r="E29" t="n">
-        <v>1.61</v>
+        <v>6.91</v>
       </c>
       <c r="F29" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="G29" t="n">
-        <v>13296</v>
+        <v>7.46</v>
       </c>
       <c r="H29" t="n">
-        <v>18.18</v>
+        <v>0.11</v>
       </c>
       <c r="I29" t="n">
-        <v>85.78</v>
+        <v>1010</v>
       </c>
       <c r="J29" t="n">
-        <v>53.42</v>
+        <v>-5.14</v>
       </c>
       <c r="K29" t="n">
-        <v>59.34</v>
+        <v>15.7</v>
       </c>
       <c r="L29" t="n">
-        <v>6.63</v>
+        <v>12.89</v>
       </c>
       <c r="M29" t="n">
-        <v>496415.88</v>
+        <v>5.74</v>
       </c>
       <c r="N29" t="n">
-        <v>36.74</v>
+        <v>1381712.03</v>
       </c>
       <c r="O29" t="n">
-        <v>12.61</v>
+        <v>46.26</v>
       </c>
       <c r="P29" t="n">
-        <v>3.81</v>
+        <v>14.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>110519</v>
+        <v>2.58</v>
       </c>
       <c r="R29" t="n">
-        <v>15401</v>
+        <v>6427</v>
       </c>
       <c r="S29" t="n">
-        <v>-7745</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U29" t="n">
-        <v>19</v>
+        <v>2724</v>
+      </c>
+      <c r="T29" t="n">
+        <v>33</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
       </c>
       <c r="V29" t="n">
-        <v>16.30293930023252</v>
+        <v>45</v>
+      </c>
+      <c r="W29" t="n">
+        <v>41.79973191512695</v>
+      </c>
+      <c r="X29" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>5.883921200220743</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2608,72 +2875,81 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11.55</v>
+        <v>3347</v>
       </c>
       <c r="D30" t="n">
-        <v>0.76</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>5.22</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>1.17</v>
+        <v>0.08</v>
       </c>
       <c r="G30" t="n">
-        <v>925</v>
+        <v>19.83</v>
       </c>
       <c r="H30" t="n">
-        <v>9.210000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="I30" t="n">
-        <v>7.56</v>
+        <v>1929</v>
       </c>
       <c r="J30" t="n">
-        <v>5.92</v>
+        <v>10.33</v>
       </c>
       <c r="K30" t="n">
-        <v>58.02</v>
+        <v>11.29</v>
       </c>
       <c r="L30" t="n">
-        <v>13.7</v>
+        <v>10.68</v>
       </c>
       <c r="M30" t="n">
-        <v>146151.16</v>
+        <v>14.8</v>
       </c>
       <c r="N30" t="n">
-        <v>9.539999999999999</v>
+        <v>3154358.33</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>25.87</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>1.21</v>
       </c>
       <c r="Q30" t="n">
-        <v>98692</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>3020</v>
+        <v>20521</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U30" t="n">
-        <v>20</v>
+        <v>1733</v>
+      </c>
+      <c r="T30" t="n">
+        <v>22</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
       </c>
       <c r="V30" t="n">
-        <v>19.82084189180693</v>
+        <v>16</v>
+      </c>
+      <c r="W30" t="n">
+        <v>38.11747535171825</v>
+      </c>
+      <c r="X30" t="n">
+        <v>27.25430316031267</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14.80997180241832</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2682,72 +2958,81 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.04</v>
+        <v>158788</v>
       </c>
       <c r="D31" t="n">
-        <v>8.380000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>1.32</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.05</v>
+        <v>0.58</v>
       </c>
       <c r="G31" t="n">
-        <v>7906</v>
+        <v>7.73</v>
       </c>
       <c r="H31" t="n">
-        <v>19.07</v>
+        <v>0.51</v>
       </c>
       <c r="I31" t="n">
-        <v>23.25</v>
+        <v>45207</v>
       </c>
       <c r="J31" t="n">
-        <v>20.11</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>49.7</v>
+        <v>14.68</v>
       </c>
       <c r="L31" t="n">
-        <v>5.73</v>
+        <v>11.95</v>
       </c>
       <c r="M31" t="n">
-        <v>2618348.58</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>9.81</v>
+        <v>432472.71</v>
       </c>
       <c r="O31" t="n">
-        <v>3.91</v>
+        <v>58.34</v>
       </c>
       <c r="P31" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>26645</v>
+        <v>4.21</v>
       </c>
       <c r="R31" t="n">
-        <v>6412</v>
+        <v>899041</v>
       </c>
       <c r="S31" t="n">
-        <v>100</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U31" t="n">
-        <v>31</v>
+        <v>79020</v>
+      </c>
+      <c r="T31" t="n">
+        <v>18</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
       </c>
       <c r="V31" t="n">
-        <v>19.10193873049559</v>
+        <v>10</v>
+      </c>
+      <c r="W31" t="n">
+        <v>36.68282246218183</v>
+      </c>
+      <c r="X31" t="n">
+        <v>17.28975659693698</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>24.46173600944801</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2756,66 +3041,75 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14.34</v>
+        <v>7569</v>
       </c>
       <c r="D32" t="n">
-        <v>6.81</v>
+        <v>3.06</v>
       </c>
       <c r="E32" t="n">
-        <v>1.4</v>
+        <v>11.55</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="G32" t="n">
-        <v>35669</v>
+        <v>5.22</v>
       </c>
       <c r="H32" t="n">
-        <v>21.95</v>
+        <v>1.17</v>
       </c>
       <c r="I32" t="n">
-        <v>23.87</v>
+        <v>925</v>
       </c>
       <c r="J32" t="n">
-        <v>15.42</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>49.05</v>
+        <v>7.56</v>
       </c>
       <c r="L32" t="n">
-        <v>7.67</v>
+        <v>5.92</v>
       </c>
       <c r="M32" t="n">
-        <v>808359.03</v>
+        <v>13.7</v>
       </c>
       <c r="N32" t="n">
-        <v>49.42</v>
+        <v>146151.16</v>
       </c>
       <c r="O32" t="n">
-        <v>4.4</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="P32" t="n">
-        <v>4.33</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>283649</v>
+        <v>2.18</v>
       </c>
       <c r="R32" t="n">
-        <v>65446</v>
+        <v>98692</v>
       </c>
       <c r="S32" t="n">
-        <v>-44685</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U32" t="n">
-        <v>23</v>
+        <v>3020</v>
+      </c>
+      <c r="T32" t="n">
+        <v>9</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V32" t="n">
-        <v>30.18695614094877</v>
+        <v>20</v>
+      </c>
+      <c r="W32" t="n">
+        <v>34.24436618882645</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>19.82084189180693</v>
       </c>
     </row>
   </sheetData>
